--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486351_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486351_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8888</v>
+        <v>4.8455</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0309</v>
+        <v>1.9877</v>
       </c>
       <c r="F2" t="n">
         <v>2.8578</v>
@@ -610,10 +610,10 @@
         <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1887</v>
+        <v>0.1454</v>
       </c>
       <c r="U2" t="n">
         <v>0.4398</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. DE BISSCHOP</t>
+          <t>V. ALVES BENITE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3353</v>
+        <v>3.7278</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.9379</v>
+        <v>1.735</v>
       </c>
       <c r="F3" t="n">
-        <v>5.2732</v>
+        <v>1.9928</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7993</v>
+        <v>1.908</v>
       </c>
       <c r="H3" t="n">
-        <v>3.0902</v>
+        <v>2.1925</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7092000000000001</v>
+        <v>-0.2844</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7899</v>
+        <v>1.494</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6369</v>
+        <v>1.7186</v>
       </c>
       <c r="L3" t="n">
-        <v>0.153</v>
+        <v>-0.2246</v>
       </c>
       <c r="M3" t="n">
-        <v>2.0095</v>
+        <v>0.4141</v>
       </c>
       <c r="N3" t="n">
-        <v>1.4533</v>
+        <v>0.4739</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5562</v>
+        <v>-0.0598</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>1.493</v>
+        <v>-0.0279</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0959</v>
+        <v>-0.5191</v>
       </c>
       <c r="U3" t="n">
-        <v>2.5889</v>
+        <v>0.4912</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.7395</v>
+        <v>0.7602</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.5443</v>
+        <v>0.7602</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. ALVES BENITE</t>
+          <t>B. DE BISSCHOP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2297</v>
+        <v>3.6294</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8842</v>
+        <v>-0.5341</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3455</v>
+        <v>4.1635</v>
       </c>
       <c r="G4" t="n">
-        <v>1.908</v>
+        <v>3.7993</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1925</v>
+        <v>3.0902</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2844</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>1.494</v>
+        <v>1.7899</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7186</v>
+        <v>1.6369</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2246</v>
+        <v>0.153</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4141</v>
+        <v>2.0095</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4739</v>
+        <v>1.4533</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0598</v>
+        <v>0.5562</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.526</v>
+        <v>0.7871</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3699</v>
+        <v>-0.6922</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1561</v>
+        <v>1.4793</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7602</v>
+        <v>-0.7395</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7602</v>
+        <v>-0.5443</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1725</v>
+        <v>2.6696</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9875</v>
+        <v>1.5463</v>
       </c>
       <c r="F5" t="n">
-        <v>1.185</v>
+        <v>1.1233</v>
       </c>
       <c r="G5" t="n">
         <v>3.072</v>
@@ -844,13 +844,13 @@
         <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0358</v>
+        <v>0.5329</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.1262</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7208</v>
+        <v>0.6591</v>
       </c>
       <c r="V5" t="n">
         <v>0.3698</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. KASIBABU SHILALA</t>
+          <t>P. RIGOT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5002</v>
+        <v>1.3929</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0344</v>
+        <v>-0.0514</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4658</v>
+        <v>1.4444</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4371</v>
+        <v>-1.5681</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5272</v>
+        <v>-1.2805</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0901</v>
+        <v>-0.2877</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9321</v>
+        <v>-2.172</v>
       </c>
       <c r="K6" t="n">
-        <v>2.6644</v>
+        <v>-0.7966</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2677</v>
+        <v>-1.3754</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4951</v>
+        <v>0.6038</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1372</v>
+        <v>-0.4838</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3578</v>
+        <v>1.0877</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.6976</v>
+        <v>0.435</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.5676</v>
+        <v>-0.2175</v>
       </c>
       <c r="R6" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5655</v>
+        <v>-0.1036</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3447</v>
+        <v>0.0781</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2208</v>
+        <v>-0.1818</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1952</v>
+        <v>2.6297</v>
       </c>
       <c r="W6" t="n">
-        <v>1.3252</v>
+        <v>2.2599</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.13</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. RIGOT</t>
+          <t>D. STOLBETSKIY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0153</v>
+        <v>0.4824</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.275</v>
+        <v>0.4455</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2902</v>
+        <v>0.0369</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5681</v>
+        <v>-1.009</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2805</v>
+        <v>-0.9245</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2877</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.172</v>
+        <v>-0.7086</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7966</v>
+        <v>-0.7086</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3754</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6038</v>
+        <v>-0.3004</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4838</v>
+        <v>-0.216</v>
       </c>
       <c r="O7" t="n">
-        <v>1.0877</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P7" t="n">
         <v>0.435</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4813</v>
+        <v>-0.0736</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1454</v>
+        <v>0.024</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3359</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>2.6297</v>
+        <v>1.13</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2599</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. STOLBETSKIY</t>
+          <t>J. KASIBABU SHILALA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8986</v>
+        <v>0.3356</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8925</v>
+        <v>0.2088</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0061</v>
+        <v>0.1267</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.009</v>
+        <v>2.4371</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9245</v>
+        <v>2.5272</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.0901</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7086</v>
+        <v>2.9321</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7086</v>
+        <v>2.6644</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.2677</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3004</v>
+        <v>-0.4951</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.216</v>
+        <v>-0.1372</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.3578</v>
       </c>
       <c r="P8" t="n">
-        <v>0.435</v>
+        <v>-3.6976</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-4.5676</v>
       </c>
       <c r="R8" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3426</v>
+        <v>1.4009</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4711</v>
+        <v>0.5191</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1285</v>
+        <v>0.8817</v>
       </c>
       <c r="V8" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>1.3252</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="9">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2258</v>
+        <v>-0.9184</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9764</v>
+        <v>-3.1314</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7506</v>
+        <v>2.213</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9055</v>
@@ -1312,13 +1312,13 @@
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1027</v>
+        <v>0.2046</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4194</v>
+        <v>-0.5744</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3166</v>
+        <v>0.779</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.9914</v>
+        <v>-2.9992</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.5736</v>
+        <v>-2.7971</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4178</v>
+        <v>-0.2021</v>
       </c>
       <c r="G13" t="n">
         <v>-2.0957</v>
@@ -1468,13 +1468,13 @@
         <v>0.6525</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4539</v>
+        <v>0.4461</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5997</v>
+        <v>0.3761</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1458</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>0.3904</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.7412</v>
+        <v>11.0836</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.0209</v>
+        <v>-1.6782</v>
       </c>
       <c r="F14" t="n">
-        <v>12.7619</v>
+        <v>12.7618</v>
       </c>
       <c r="G14" t="n">
         <v>8.438400000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>3.9681</v>
+        <v>3.968099999999998</v>
       </c>
       <c r="I14" t="n">
-        <v>4.470300000000002</v>
+        <v>4.470300000000001</v>
       </c>
       <c r="J14" t="n">
         <v>5.647200000000001</v>
@@ -1525,7 +1525,7 @@
         <v>3.0134</v>
       </c>
       <c r="L14" t="n">
-        <v>2.633800000000001</v>
+        <v>2.633799999999999</v>
       </c>
       <c r="M14" t="n">
         <v>2.7912</v>
@@ -1546,13 +1546,13 @@
         <v>7.6125</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9623</v>
+        <v>3.3047</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1114</v>
+        <v>-0.7692</v>
       </c>
       <c r="U14" t="n">
-        <v>4.0736</v>
+        <v>4.073700000000001</v>
       </c>
       <c r="V14" t="n">
         <v>5.865799999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.346</v>
+        <v>4.5888</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7285</v>
+        <v>1.0637</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6175</v>
+        <v>3.5251</v>
       </c>
       <c r="G15" t="n">
         <v>3.4746</v>
@@ -1624,13 +1624,13 @@
         <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9557</v>
+        <v>-0.7129</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0274</v>
+        <v>-0.6922</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0717</v>
+        <v>-0.0207</v>
       </c>
       <c r="V15" t="n">
         <v>0.7395</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1037</v>
+        <v>1.7067</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1991</v>
+        <v>-0.5344</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3027</v>
+        <v>2.2411</v>
       </c>
       <c r="G16" t="n">
         <v>2.0726</v>
@@ -1702,13 +1702,13 @@
         <v>2.3926</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1865</v>
+        <v>-0.5834</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5407</v>
+        <v>-0.876</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3542</v>
+        <v>0.2926</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0173</v>
+        <v>1.4874</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5567</v>
+        <v>-0.3332</v>
       </c>
       <c r="F17" t="n">
-        <v>1.574</v>
+        <v>1.8206</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3475</v>
@@ -1780,13 +1780,13 @@
         <v>1.9576</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5276</v>
+        <v>-1.0575</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1043</v>
+        <v>-0.8808</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4232</v>
+        <v>-0.1767</v>
       </c>
       <c r="V17" t="n">
         <v>0.9347</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. HUGUET CARRASCO</t>
+          <t>R. GILL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8266</v>
+        <v>0.1208</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5002</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3268</v>
+        <v>0.7755</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9377</v>
+        <v>-0.2335</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2106</v>
+        <v>-0.6264</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.1483</v>
+        <v>0.3928</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6324</v>
+        <v>-1.3873</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4115</v>
+        <v>-1.502</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.0439</v>
+        <v>0.1147</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3053</v>
+        <v>1.1538</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2009</v>
+        <v>0.8757</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1044</v>
+        <v>0.2781</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>1.307</v>
+        <v>-0.1682</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2197</v>
+        <v>-0.0276</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0872</v>
+        <v>-0.1406</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1952</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1952</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. GILL</t>
+          <t>S. HUGUET CARRASCO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6796</v>
+        <v>0.0057</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0959</v>
+        <v>-1.506</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7755</v>
+        <v>1.5117</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2335</v>
+        <v>-0.9377</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6264</v>
+        <v>1.2106</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3928</v>
+        <v>-2.1483</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3873</v>
+        <v>-0.6324</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.502</v>
+        <v>1.4115</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1147</v>
+        <v>-2.0439</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1538</v>
+        <v>-0.3053</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8757</v>
+        <v>-0.2009</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2781</v>
+        <v>-0.1044</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3906</v>
+        <v>0.4861</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5312</v>
+        <v>0.2139</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1406</v>
+        <v>0.2722</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.1952</v>
       </c>
       <c r="W19" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3252</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. OKANU</t>
+          <t>M. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0694</v>
+        <v>-1.1385</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6563</v>
+        <v>0.1285</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5869</v>
+        <v>-1.267</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9087</v>
+        <v>-0.3892</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2951</v>
+        <v>-0.2585</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6136</v>
+        <v>-0.1307</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3745</v>
+        <v>0.2787</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1833</v>
+        <v>0.2404</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1912</v>
+        <v>0.0382</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2832</v>
+        <v>-0.6679</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4783</v>
+        <v>-0.4989</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.1689</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.435</v>
+        <v>0.435</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7401</v>
+        <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2743</v>
+        <v>-0.0544</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1442</v>
+        <v>-0.1502</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1301</v>
+        <v>0.0958</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. IGLESIAS FERNANDEZ</t>
+          <t>C. OKANU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2811</v>
+        <v>-2.1214</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0167</v>
+        <v>-2.2151</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2978</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3892</v>
+        <v>-1.9087</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2585</v>
+        <v>-1.2951</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1307</v>
+        <v>-0.6136</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2787</v>
+        <v>0.3745</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2404</v>
+        <v>0.1833</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0382</v>
+        <v>0.1912</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6679</v>
+        <v>-2.2832</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4989</v>
+        <v>-1.4783</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1689</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>0.435</v>
+        <v>-0.435</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
-        <v>0.435</v>
+        <v>1.7401</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.197</v>
+        <v>0.2223</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.262</v>
+        <v>-0.4146</v>
       </c>
       <c r="U21" t="n">
-        <v>0.065</v>
+        <v>0.6369</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. MC DONNELL</t>
+          <t>G. KALSCHEUR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1939</v>
+        <v>-3.9446</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1827</v>
+        <v>-2.7398</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0112</v>
+        <v>-1.2048</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.2454</v>
+        <v>-3.4919</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7027</v>
+        <v>-2.8433</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.5428</v>
+        <v>-0.6486</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.3727</v>
+        <v>-1.3776</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2523</v>
+        <v>-1.5139</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.1204</v>
+        <v>0.1363</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8727</v>
+        <v>-2.1143</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4504</v>
+        <v>-1.3293</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4224</v>
+        <v>-0.7849</v>
       </c>
       <c r="P22" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9283</v>
+        <v>-0.0829</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8099</v>
+        <v>-0.4698</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1184</v>
+        <v>0.3869</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.3252</v>
+        <v>-0.3698</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.3252</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. KALSCHEUR</t>
+          <t>S. MC DONNELL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6151</v>
+        <v>-4.0128</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4103</v>
+        <v>-2.8474</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2048</v>
+        <v>-1.1654</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.4919</v>
+        <v>-3.2454</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.8433</v>
+        <v>-0.7027</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6486</v>
+        <v>-2.5428</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3776</v>
+        <v>-2.3727</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5139</v>
+        <v>-0.2523</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1363</v>
+        <v>-2.1204</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.1143</v>
+        <v>-0.8727</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3293</v>
+        <v>-0.4504</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7849</v>
+        <v>-0.4224</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.305</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.7472</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1404</v>
+        <v>-0.4747</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3869</v>
+        <v>-0.2725</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3698</v>
+        <v>-1.3252</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.554600000000001</v>
+        <v>-7.4333</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.9058</v>
+        <v>-3.1235</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.6488</v>
+        <v>-4.3098</v>
       </c>
       <c r="G24" t="n">
         <v>-3.4318</v>
@@ -2326,13 +2326,13 @@
         <v>1.305</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3854</v>
+        <v>-0.2641</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0839</v>
+        <v>-0.3016</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3015</v>
+        <v>0.0375</v>
       </c>
       <c r="V24" t="n">
         <v>-3.9549</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.7409</v>
+        <v>-10.7412</v>
       </c>
       <c r="E25" t="n">
-        <v>-12.7618</v>
+        <v>-12.7619</v>
       </c>
       <c r="F25" t="n">
-        <v>2.020800000000001</v>
+        <v>2.0207</v>
       </c>
       <c r="G25" t="n">
-        <v>-8.438499999999998</v>
+        <v>-8.438499999999999</v>
       </c>
       <c r="H25" t="n">
         <v>-3.9682</v>
@@ -2380,7 +2380,7 @@
         <v>-2.791199999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.9544999999999997</v>
+        <v>-0.9545000000000002</v>
       </c>
       <c r="L25" t="n">
         <v>-1.8365</v>
@@ -2395,7 +2395,7 @@
         <v>-2.6338</v>
       </c>
       <c r="P25" t="n">
-        <v>6.5251</v>
+        <v>6.525099999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-7.6127</v>
@@ -2404,10 +2404,10 @@
         <v>14.1379</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.9621</v>
+        <v>-2.9622</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.0735</v>
+        <v>-4.0736</v>
       </c>
       <c r="U25" t="n">
         <v>1.1114</v>
@@ -2419,7 +2419,7 @@
         <v>1.7156</v>
       </c>
       <c r="X25" t="n">
-        <v>-7.581399999999999</v>
+        <v>-7.5814</v>
       </c>
     </row>
   </sheetData>
